--- a/pharmacy/assets/template.xlsx
+++ b/pharmacy/assets/template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,9 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -64,8 +65,14 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -147,11 +154,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -210,6 +247,18 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5000"/>
+  <dimension ref="A1:N5000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -648,6 +697,7 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15.88671875" customWidth="1" min="11" max="11"/>
     <col width="13.21875" customWidth="1" min="12" max="12"/>
+    <col width="66" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -670,6 +720,11 @@
       </c>
       <c r="K1" s="22" t="n"/>
       <c r="L1" s="23" t="n"/>
+      <c r="N1" s="28" t="inlineStr">
+        <is>
+          <t>ПРАВИЛА ЗАПОЛНЕНИЯ</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
@@ -723,6 +778,11 @@
           <t>Количество</t>
         </is>
       </c>
+      <c r="N2" s="29" t="inlineStr">
+        <is>
+          <t>Моя аптечка (левая таблица)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="n"/>
@@ -736,6 +796,11 @@
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
       <c r="L3" s="15" t="n"/>
+      <c r="N3" s="30" t="inlineStr">
+        <is>
+          <t>• Обязательно: Название, Категория, Количество.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="n"/>
@@ -750,6 +815,11 @@
       <c r="J4" s="18" t="n"/>
       <c r="K4" s="18" t="n"/>
       <c r="L4" s="18" t="n"/>
+      <c r="N4" s="30" t="inlineStr">
+        <is>
+          <t>• Категория и Ед.изм.: выберите из списка в ячейке.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="n"/>
@@ -763,6 +833,11 @@
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
+      <c r="N5" s="30" t="inlineStr">
+        <is>
+          <t>• Количество: число, дробное через запятую или точку.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="n"/>
@@ -777,28 +852,58 @@
       <c r="J6" s="18" t="n"/>
       <c r="K6" s="18" t="n"/>
       <c r="L6" s="18" t="n"/>
+      <c r="N6" s="30" t="inlineStr">
+        <is>
+          <t>• Срок годности: ДД.ММ.ГГГГ (например, 31.12.2027) или пусто.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="F7" s="26" t="n"/>
       <c r="H7" s="3" t="n"/>
+      <c r="N7" s="30" t="inlineStr">
+        <is>
+          <t>• Дата добавления: ставит программа, заполнять не нужно.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="F8" s="26" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
+      <c r="N8" s="29" t="inlineStr">
+        <is>
+          <t>Список покупок (правая таблица)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="F9" s="26" t="n"/>
       <c r="H9" s="3" t="n"/>
+      <c r="N9" s="30" t="inlineStr">
+        <is>
+          <t>• Обязательно: Товар. Количество по умолчанию 1.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="F10" s="26" t="n"/>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
+      <c r="N10" s="30" t="inlineStr">
+        <is>
+          <t>Заполняйте строки подряд, без пропусков: рамки и цвет продолжаются сами.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="F11" s="26" t="n"/>
       <c r="H11" s="3" t="n"/>
+      <c r="N11" s="31" t="inlineStr">
+        <is>
+          <t>Строки с ошибкой программа пропустит и покажет, какие именно.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="F12" s="26" t="n"/>
@@ -17650,13 +17755,20 @@
       <formula>AND(COUNTA($J7:$L7)&gt;0,MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation sqref="C3:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Неверное значение" error="Выберите значение из списка" type="list">
+  <dataValidations count="9">
+    <dataValidation sqref="C3:C5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Неверное значение" error="Выберите значение из списка" promptTitle="Выберите из списка" prompt="Нажмите на стрелку справа" type="list">
       <formula1>='Подсказки'!$D$2:$D$5</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Неверное значение" error="Выберите значение из списка" type="list">
+    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Неверное значение" error="Выберите значение из списка" promptTitle="Выберите из списка" prompt="Нажмите на стрелку справа" type="list">
       <formula1>='Подсказки'!$E$2:$E$8</formula1>
     </dataValidation>
+    <dataValidation sqref="A3:A5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Название" prompt="Обязательно"/>
+    <dataValidation sqref="B3:B5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Дата добавления" prompt="Не заполняйте: программа поставит её сама"/>
+    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Количество" prompt="Обязательно. Число, например 2 или 1,5"/>
+    <dataValidation sqref="F3:F5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Срок годности" prompt="ДД.ММ.ГГГГ, например 31.12.2027, или пусто"/>
+    <dataValidation sqref="J3:J5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Товар" prompt="Обязательно"/>
+    <dataValidation sqref="K3:K5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Дата добавления" prompt="Не заполняйте: программа поставит её сама"/>
+    <dataValidation sqref="L3:L5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Количество" prompt="Число. Если пусто, будет 1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17683,7 +17795,6 @@
           <t>Как заполнять</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
       <c r="D1" s="27" t="inlineStr">
         <is>
           <t>Категории</t>

--- a/pharmacy/assets/template.xlsx
+++ b/pharmacy/assets/template.xlsx
@@ -32,7 +32,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +63,24 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0093CDDD"/>
+        <bgColor rgb="0093CDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7DEE8"/>
+        <bgColor rgb="00B7DEE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEEF4"/>
+        <bgColor rgb="00DBEEF4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -111,11 +129,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -143,6 +169,28 @@
         <patternFill patternType="solid">
           <fgColor rgb="00FFFFFF"/>
           <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DBEEF4"/>
+          <bgColor rgb="00DBEEF4"/>
         </patternFill>
       </fill>
       <border>
@@ -15794,36 +15842,36 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>СПИСОК ПОКУПОК</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
+      <c r="B1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
+      <c r="A3" s="15" t="n"/>
+      <c r="B3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n"/>
       <c r="B4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n"/>
@@ -15834,7 +15882,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:B5000">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="2">
       <formula>AND(COUNTA($A7:$B7)&gt;0,MOD(ROW(),2)=1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">

--- a/pharmacy/assets/template.xlsx
+++ b/pharmacy/assets/template.xlsx
@@ -289,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -416,6 +416,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -852,190 +855,102 @@
   <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="120" customWidth="1" style="16" min="1" max="1"/>
+    <col width="150" customWidth="1" style="16" min="1" max="1"/>
     <col width="8.88671875" customWidth="1" min="2" max="2"/>
     <col width="8.88671875" customWidth="1" min="3" max="3"/>
     <col width="8.88671875" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="48" t="inlineStr">
+    <row r="1" ht="409" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
         <is>
-          <t>ПРАВИЛА ЗАПОЛНЕНИЯ</t>
+          <t>ПРАВИЛА ЗАПОЛНЕНИЯ
+ОБЩИЕ: заполняйте строки подряд, без пустых строк между ними. Не переименовывайте листы и заголовки столбцов. Строка с ошибкой пропускается, остальные добавляются, а после импорта программа покажет причины. Дату добавления программа ставит сама.
+ЛИСТ «МОЯ АПТЕЧКА»: Название обязательно, до 100 символов. Категория обязательна, из списка: Лекарства, Медицинские товары, Бытовая химия, Средства гигиены. Количество обязательно, число от 0 до 1 000 000, дробное через запятую или точку (1,5), без минуса. Ед.изм. из списка: шт., упак., табл., мг, г, мл, фл. (пусто = шт.). Срок годности в виде ДД.ММ.ГГГГ, например 31.12.2027, или пусто. Место хранения не обязательно, до 100 символов.
+ЛИСТ «СПИСОК ПОКУПОК»: Товар обязателен, до 100 символов. Количество больше 0 и не больше 1 000 000 (пусто = 1). Единица всегда «шт.».
+СТРОКА НЕ ИМПОРТИРУЕТСЯ, ЕСЛИ: не заполнено обязательное поле; категория или единица не из списка; количество не число, отрицательное, больше 1 000 000 (в списке покупок ещё и 0); дата записана не как ДД.ММ.ГГГГ или такой даты нет; текст длиннее допустимого.</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="49" t="inlineStr">
-        <is>
-          <t>Общие правила</t>
-        </is>
-      </c>
+      <c r="A2" s="49" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
-        <is>
-          <t>• Заполняйте строки подряд, без пустых строк между ними: рамки и цвет продолжаются сами.</t>
-        </is>
-      </c>
+      <c r="A3" s="50" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="inlineStr">
-        <is>
-          <t>• Не переименовывайте листы и заголовки столбцов: по ним программа находит данные.</t>
-        </is>
-      </c>
+      <c r="A4" s="50" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
-        <is>
-          <t>• Строка с ошибкой пропускается, остальные добавляются. После импорта программа покажет, сколько добавлено и по какой причине строки пропущены.</t>
-        </is>
-      </c>
+      <c r="A5" s="50" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
-        <is>
-          <t>• Дату добавления программа ставит сама, в таблицах её нет.</t>
-        </is>
-      </c>
+      <c r="A6" s="50" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="51" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="inlineStr">
-        <is>
-          <t>Лист «Моя аптечка»</t>
-        </is>
-      </c>
+      <c r="A8" s="49" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
-        <is>
-          <t>• Название: обязательно, не длиннее 100 символов.</t>
-        </is>
-      </c>
+      <c r="A9" s="50" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
-        <is>
-          <t>• Категория: обязательно, выбирается из списка: Лекарства, Медицинские товары, Бытовая химия, Средства гигиены.</t>
-        </is>
-      </c>
+      <c r="A10" s="50" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
-        <is>
-          <t>• Количество: обязательно, число от 0 до 1 000 000. Дробные числа через запятую или точку (например, 1,5). Отрицательные числа нельзя.</t>
-        </is>
-      </c>
+      <c r="A11" s="51" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="inlineStr">
-        <is>
-          <t>• Ед.изм.: выбирается из списка: шт., упак., табл., мг, г, мл, фл. Если оставить пустой, будет «шт.».</t>
-        </is>
-      </c>
+      <c r="A12" s="52" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="inlineStr">
-        <is>
-          <t>• Срок годности: дата в виде ДД.ММ.ГГГГ (например, 31.12.2027). Если срока нет, оставьте пустым.</t>
-        </is>
-      </c>
+      <c r="A13" s="52" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="inlineStr">
-        <is>
-          <t>• Место хранения: необязательно, не длиннее 100 символов.</t>
-        </is>
-      </c>
+      <c r="A14" s="52" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="52" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="inlineStr">
-        <is>
-          <t>Лист «Список покупок»</t>
-        </is>
-      </c>
+      <c r="A16" s="53" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="inlineStr">
-        <is>
-          <t>• Товар: обязательно, не длиннее 100 символов.</t>
-        </is>
-      </c>
+      <c r="A17" s="52" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="52" t="inlineStr">
-        <is>
-          <t>• Количество: число больше 0, но не больше 1 000 000 (дробные через запятую или точку). Если оставить пустым, будет 1.</t>
-        </is>
-      </c>
+      <c r="A18" s="52" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="52" t="inlineStr">
-        <is>
-          <t>• Единица измерения здесь не указывается: ставится «шт.».</t>
-        </is>
-      </c>
+      <c r="A19" s="52" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
-        <is>
-          <t>Причины, по которым строка не импортируется</t>
-        </is>
-      </c>
+      <c r="A21" s="53" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="52" t="inlineStr">
-        <is>
-          <t>• Не заполнено обязательное поле (название, категория или количество).</t>
-        </is>
-      </c>
+      <c r="A22" s="52" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="52" t="inlineStr">
-        <is>
-          <t>• Категория не из списка или написана иначе.</t>
-        </is>
-      </c>
+      <c r="A23" s="52" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="52" t="inlineStr">
-        <is>
-          <t>• Единица измерения не из списка.</t>
-        </is>
-      </c>
+      <c r="A24" s="52" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="52" t="inlineStr">
-        <is>
-          <t>• Количество не число, отрицательное, больше 1 000 000 (в списке покупок ещё и равно 0).</t>
-        </is>
-      </c>
+      <c r="A25" s="52" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="inlineStr">
-        <is>
-          <t>• Дата записана не как ДД.ММ.ГГГГ или такой даты нет в календаре.</t>
-        </is>
-      </c>
+      <c r="A26" s="52" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="inlineStr">
-        <is>
-          <t>• Текст длиннее допустимого.</t>
-        </is>
-      </c>
+      <c r="A27" s="52" t="n"/>
     </row>
     <row r="28"/>
     <row r="29"/>

--- a/pharmacy/assets/template.xlsx
+++ b/pharmacy/assets/template.xlsx
@@ -289,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -416,9 +416,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -855,102 +852,190 @@
   <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="150" customWidth="1" style="16" min="1" max="1"/>
+    <col width="120" customWidth="1" style="16" min="1" max="1"/>
     <col width="8.88671875" customWidth="1" min="2" max="2"/>
     <col width="8.88671875" customWidth="1" min="3" max="3"/>
     <col width="8.88671875" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="409" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="48" t="inlineStr">
         <is>
-          <t>ПРАВИЛА ЗАПОЛНЕНИЯ
-ОБЩИЕ: заполняйте строки подряд, без пустых строк между ними. Не переименовывайте листы и заголовки столбцов. Строка с ошибкой пропускается, остальные добавляются, а после импорта программа покажет причины. Дату добавления программа ставит сама.
-ЛИСТ «МОЯ АПТЕЧКА»: Название обязательно, до 100 символов. Категория обязательна, из списка: Лекарства, Медицинские товары, Бытовая химия, Средства гигиены. Количество обязательно, число от 0 до 1 000 000, дробное через запятую или точку (1,5), без минуса. Ед.изм. из списка: шт., упак., табл., мг, г, мл, фл. (пусто = шт.). Срок годности в виде ДД.ММ.ГГГГ, например 31.12.2027, или пусто. Место хранения не обязательно, до 100 символов.
-ЛИСТ «СПИСОК ПОКУПОК»: Товар обязателен, до 100 символов. Количество больше 0 и не больше 1 000 000 (пусто = 1). Единица всегда «шт.».
-СТРОКА НЕ ИМПОРТИРУЕТСЯ, ЕСЛИ: не заполнено обязательное поле; категория или единица не из списка; количество не число, отрицательное, больше 1 000 000 (в списке покупок ещё и 0); дата записана не как ДД.ММ.ГГГГ или такой даты нет; текст длиннее допустимого.</t>
+          <t>ПРАВИЛА ЗАПОЛНЕНИЯ</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="49" t="n"/>
+      <c r="A2" s="49" t="inlineStr">
+        <is>
+          <t>Общие правила</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="n"/>
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>• Заполняйте строки подряд, без пустых строк между ними: рамки и цвет продолжаются сами.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="n"/>
+      <c r="A4" s="50" t="inlineStr">
+        <is>
+          <t>• Не переименовывайте листы и заголовки столбцов: по ним программа находит данные.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="n"/>
+      <c r="A5" s="50" t="inlineStr">
+        <is>
+          <t>• Строка с ошибкой пропускается, остальные добавляются. После импорта программа покажет, сколько добавлено и по какой причине строки пропущены.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="n"/>
+      <c r="A6" s="50" t="inlineStr">
+        <is>
+          <t>• Дату добавления программа ставит сама, в таблицах её нет.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="51" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="n"/>
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>Лист «Моя аптечка»</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="n"/>
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>• Название: обязательно, не длиннее 100 символов.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="n"/>
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>• Категория: обязательно, выбирается из списка: Лекарства, Медицинские товары, Бытовая химия, Средства гигиены.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="n"/>
+      <c r="A11" s="51" t="inlineStr">
+        <is>
+          <t>• Количество: обязательно, число от 0 до 1 000 000. Дробные числа через запятую или точку (например, 1,5). Отрицательные числа нельзя.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="n"/>
+      <c r="A12" s="52" t="inlineStr">
+        <is>
+          <t>• Ед.изм.: выбирается из списка: шт., упак., табл., мг, г, мл, фл. Если оставить пустой, будет «шт.».</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="n"/>
+      <c r="A13" s="52" t="inlineStr">
+        <is>
+          <t>• Срок годности: дата в виде ДД.ММ.ГГГГ (например, 31.12.2027). Если срока нет, оставьте пустым.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="n"/>
+      <c r="A14" s="52" t="inlineStr">
+        <is>
+          <t>• Место хранения: необязательно, не длиннее 100 символов.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="52" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="n"/>
+      <c r="A16" s="53" t="inlineStr">
+        <is>
+          <t>Лист «Список покупок»</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="n"/>
+      <c r="A17" s="52" t="inlineStr">
+        <is>
+          <t>• Товар: обязательно, не длиннее 100 символов.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="52" t="n"/>
+      <c r="A18" s="52" t="inlineStr">
+        <is>
+          <t>• Количество: число больше 0, но не больше 1 000 000 (дробные через запятую или точку). Если оставить пустым, будет 1.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="52" t="n"/>
+      <c r="A19" s="52" t="inlineStr">
+        <is>
+          <t>• Единица измерения здесь не указывается: ставится «шт.».</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="n"/>
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>Причины, по которым строка не импортируется</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="52" t="n"/>
+      <c r="A22" s="52" t="inlineStr">
+        <is>
+          <t>• Не заполнено обязательное поле (название, категория или количество).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="52" t="n"/>
+      <c r="A23" s="52" t="inlineStr">
+        <is>
+          <t>• Категория не из списка или написана иначе.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="52" t="n"/>
+      <c r="A24" s="52" t="inlineStr">
+        <is>
+          <t>• Единица измерения не из списка.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="52" t="n"/>
+      <c r="A25" s="52" t="inlineStr">
+        <is>
+          <t>• Количество не число, отрицательное, больше 1 000 000 (в списке покупок ещё и равно 0).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="n"/>
+      <c r="A26" s="52" t="inlineStr">
+        <is>
+          <t>• Дата записана не как ДД.ММ.ГГГГ или такой даты нет в календаре.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="n"/>
+      <c r="A27" s="52" t="inlineStr">
+        <is>
+          <t>• Текст длиннее допустимого.</t>
+        </is>
+      </c>
     </row>
     <row r="28"/>
     <row r="29"/>
